--- a/artfynd/A 13715-2024 artfynd.xlsx
+++ b/artfynd/A 13715-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129425710</v>
       </c>
       <c r="B2" t="n">
-        <v>56911</v>
+        <v>56916</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13715-2024 artfynd.xlsx
+++ b/artfynd/A 13715-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129425710</v>
       </c>
       <c r="B2" t="n">
-        <v>56916</v>
+        <v>56917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13715-2024 artfynd.xlsx
+++ b/artfynd/A 13715-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,132 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129839226</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56926</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tågmossen, Gunnilbo sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>550826</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6620129</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Gunnilbo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Per Eriksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Per Eriksson, Lena Öling</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13715-2024 artfynd.xlsx
+++ b/artfynd/A 13715-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129839226</v>
       </c>
       <c r="B3" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13715-2024 artfynd.xlsx
+++ b/artfynd/A 13715-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129839226</v>
       </c>
       <c r="B3" t="n">
-        <v>56927</v>
+        <v>56930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13715-2024 artfynd.xlsx
+++ b/artfynd/A 13715-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129839226</v>
       </c>
       <c r="B3" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13715-2024 artfynd.xlsx
+++ b/artfynd/A 13715-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129425710</v>
       </c>
       <c r="B2" t="n">
-        <v>57064</v>
+        <v>57066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129839226</v>
       </c>
       <c r="B3" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>131130604</v>
       </c>
       <c r="B4" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 13715-2024 artfynd.xlsx
+++ b/artfynd/A 13715-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129425710</v>
       </c>
       <c r="B2" t="n">
-        <v>57066</v>
+        <v>57067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129839226</v>
       </c>
       <c r="B3" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>131130604</v>
       </c>
       <c r="B4" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 13715-2024 artfynd.xlsx
+++ b/artfynd/A 13715-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129425710</v>
       </c>
       <c r="B2" t="n">
-        <v>57067</v>
+        <v>57070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129839226</v>
       </c>
       <c r="B3" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>131130604</v>
       </c>
       <c r="B4" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 13715-2024 artfynd.xlsx
+++ b/artfynd/A 13715-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129425710</v>
       </c>
       <c r="B2" t="n">
-        <v>57070</v>
+        <v>57071</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129839226</v>
       </c>
       <c r="B3" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>131130604</v>
       </c>
       <c r="B4" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 13715-2024 artfynd.xlsx
+++ b/artfynd/A 13715-2024 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>131130604</v>
       </c>
       <c r="B4" t="n">
-        <v>57080</v>
+        <v>57085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 13715-2024 artfynd.xlsx
+++ b/artfynd/A 13715-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1051,6 +1051,132 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132830390</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Älgstan NV hällmark, Älgstan NV hällmark, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>550790</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6619519</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gunnilbo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Eriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Eriksson, Lena Öling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13715-2024 artfynd.xlsx
+++ b/artfynd/A 13715-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129425710</v>
+        <v>129839226</v>
       </c>
       <c r="B2" t="n">
-        <v>57071</v>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -713,9 +713,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550815</v>
+        <v>550826</v>
       </c>
       <c r="R2" t="n">
-        <v>6620089</v>
+        <v>6620129</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -754,27 +759,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flög upp i vägkanten</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129839226</v>
+        <v>131130604</v>
       </c>
       <c r="B3" t="n">
-        <v>57080</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -851,14 +851,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tågmossen, Gunnilbo sn, Vstm</t>
+          <t>Tågmossen, Tågmossen, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550826</v>
+        <v>550930</v>
       </c>
       <c r="R3" t="n">
-        <v>6620129</v>
+        <v>6620382</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -885,22 +885,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131130604</v>
+        <v>132830390</v>
       </c>
       <c r="B4" t="n">
-        <v>57085</v>
+        <v>57162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,14 +977,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tågmossen, Tågmossen, Vstm</t>
+          <t>Älgstan NV hällmark, Älgstan NV hällmark, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550930</v>
+        <v>550790</v>
       </c>
       <c r="R4" t="n">
-        <v>6620382</v>
+        <v>6619519</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1011,22 +1011,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,22 +1041,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Per Eriksson</t>
+          <t>Perka Eriksson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Eriksson, Lena Öling</t>
+          <t>Perka Eriksson, Lena Öling</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132830390</v>
+        <v>129425710</v>
       </c>
       <c r="B5" t="n">
-        <v>57145</v>
+        <v>57132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1064,26 +1064,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1091,26 +1091,21 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Älgstan NV hällmark, Älgstan NV hällmark, Vstm</t>
+          <t>Tågmossen, Gunnilbo sn, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550790</v>
+        <v>550815</v>
       </c>
       <c r="R5" t="n">
-        <v>6619519</v>
+        <v>6620089</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1137,22 +1132,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flög upp i vägkanten</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,15 +1167,134 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Perka Eriksson</t>
+          <t>Per Eriksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Perka Eriksson, Lena Öling</t>
+          <t>Per Eriksson, Lena Öling</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>95105220</v>
+      </c>
+      <c r="B6" t="n">
+        <v>111399</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219716</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Krusfrö</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Selinum carvifolia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tågmossen N, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>551044</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6620484</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gunnilbo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-07-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-07-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Grusväg, dike/bryn</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
